--- a/report_forms/045_daily_patient_census_report--report_forms.xlsx
+++ b/report_forms/045_daily_patient_census_report--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>Page2 Unit</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>prophets</t>
+          <t>Page2 Prophet</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Page3 Date</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Page3 Date 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>prophets</t>
+          <t>Page4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>prophets</t>
+          <t>Page4 Prophets</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -753,7 +753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -892,57 +892,6 @@
         </is>
       </c>
       <c r="C8" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>page5_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>rn</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>RN</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>page5_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>lpn</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LPN</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>page5_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
